--- a/testResults/rescaleAlphaTimescaleResults/AlphaTimescaleTable.xlsx
+++ b/testResults/rescaleAlphaTimescaleResults/AlphaTimescaleTable.xlsx
@@ -101,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -124,30 +124,6 @@
       </bottom>
       <diagonal style="none"/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -157,15 +133,17 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -717,7 +695,7 @@
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1"/>
@@ -752,7 +730,7 @@
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>1024</v>
       </c>
       <c r="D5" s="1"/>
@@ -772,19 +750,19 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>256</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>512</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>1024</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>1024</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>1024</v>
       </c>
       <c r="H6" s="1"/>
@@ -798,34 +776,34 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="6">
-        <v>128</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C7" s="5">
+        <v>128</v>
+      </c>
+      <c r="D7" s="3">
         <v>256</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>512</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>512</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>512</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>512</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <v>512</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>512</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="4">
         <v>512</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="4">
         <v>512</v>
       </c>
     </row>
@@ -834,34 +812,34 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="6">
-        <v>128</v>
-      </c>
-      <c r="D8" s="6">
-        <v>128</v>
-      </c>
-      <c r="E8" s="6">
-        <v>128</v>
-      </c>
-      <c r="F8" s="6">
-        <v>128</v>
-      </c>
-      <c r="G8" s="6">
-        <v>128</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="C8" s="5">
+        <v>128</v>
+      </c>
+      <c r="D8" s="5">
+        <v>128</v>
+      </c>
+      <c r="E8" s="5">
+        <v>128</v>
+      </c>
+      <c r="F8" s="5">
+        <v>128</v>
+      </c>
+      <c r="G8" s="5">
+        <v>128</v>
+      </c>
+      <c r="H8" s="3">
         <v>256</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="3">
         <v>256</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>256</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="3">
         <v>256</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="3">
         <v>256</v>
       </c>
     </row>
@@ -870,34 +848,34 @@
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="6">
-        <v>128</v>
-      </c>
-      <c r="D9" s="6">
-        <v>128</v>
-      </c>
-      <c r="E9" s="6">
-        <v>128</v>
-      </c>
-      <c r="F9" s="6">
-        <v>128</v>
-      </c>
-      <c r="G9" s="6">
-        <v>128</v>
-      </c>
-      <c r="H9" s="6">
-        <v>128</v>
-      </c>
-      <c r="I9" s="6">
-        <v>128</v>
-      </c>
-      <c r="J9" s="6">
-        <v>128</v>
-      </c>
-      <c r="K9" s="6">
-        <v>128</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="C9" s="5">
+        <v>128</v>
+      </c>
+      <c r="D9" s="5">
+        <v>128</v>
+      </c>
+      <c r="E9" s="5">
+        <v>128</v>
+      </c>
+      <c r="F9" s="5">
+        <v>128</v>
+      </c>
+      <c r="G9" s="5">
+        <v>128</v>
+      </c>
+      <c r="H9" s="5">
+        <v>128</v>
+      </c>
+      <c r="I9" s="5">
+        <v>128</v>
+      </c>
+      <c r="J9" s="5">
+        <v>128</v>
+      </c>
+      <c r="K9" s="5">
+        <v>128</v>
+      </c>
+      <c r="L9" s="5">
         <v>128</v>
       </c>
     </row>
@@ -919,18 +897,175 @@
         <v>12</v>
       </c>
     </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+    </row>
     <row r="15" ht="14.25">
-      <c r="C15" s="7"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
     </row>
     <row r="16" ht="14.25">
-      <c r="C16" s="8"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
